--- a/data/externalStats/File2/TC424_Exc_External.xlsx
+++ b/data/externalStats/File2/TC424_Exc_External.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ms.ds.uhc.com\userdata\030\amitta73\Desktop\RPT_Automation\data\externalStats\File2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{604A4CAD-A8EF-4694-8C39-FEC4C1468C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3467EC8-C98C-486D-B748-ADCC9E68EBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E78BFA5E-AD37-4149-8B33-F938E55964CA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{782C8A6D-1A08-46E7-B595-36F4E35ACD46}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">Base Yr Claims </t>
   </si>
   <si>
-    <t>Forecast based on time period: 2031</t>
+    <t>Forecast based on time period: 2027</t>
   </si>
   <si>
     <t>w Exclusions</t>
@@ -107,94 +107,160 @@
     <t>Retail 90</t>
   </si>
   <si>
+    <t>HUMIRA PEN</t>
+  </si>
+  <si>
+    <t>IMMUNOMODULATORS</t>
+  </si>
+  <si>
+    <t>OHTUVAYRE</t>
+  </si>
+  <si>
+    <t>PDE3 &amp; PDE4 INHIBITORS</t>
+  </si>
+  <si>
+    <t>Mail</t>
+  </si>
+  <si>
+    <t>BREZTRI AEROSPHERE</t>
+  </si>
+  <si>
+    <t>LABA LAMA COMBO</t>
+  </si>
+  <si>
+    <t>ROZLYTREK</t>
+  </si>
+  <si>
+    <t>ONCOLOGY</t>
+  </si>
+  <si>
+    <t>Non-Specialty</t>
+  </si>
+  <si>
     <t>DUPIXENT</t>
   </si>
   <si>
     <t>CHRONIC INFLAMMATORY DISEASE</t>
   </si>
   <si>
+    <t>KISQALI</t>
+  </si>
+  <si>
+    <t>Specialty</t>
+  </si>
+  <si>
+    <t>SKYRIZI PEN</t>
+  </si>
+  <si>
+    <t>NUPLAZID</t>
+  </si>
+  <si>
+    <t>ATYPICAL ANTIPSYCHOTICS</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>TRULICITY</t>
+  </si>
+  <si>
+    <t>ONETOUCH ULTRA</t>
+  </si>
+  <si>
+    <t>DIABETES TEST STRIPS</t>
+  </si>
+  <si>
+    <t>GEMTESA</t>
+  </si>
+  <si>
+    <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+  </si>
+  <si>
+    <t>JUBBONTI</t>
+  </si>
+  <si>
+    <t>OSTEOPOROSIS AGENTS</t>
+  </si>
+  <si>
+    <t>Generic</t>
+  </si>
+  <si>
+    <t>SKYRIZI</t>
+  </si>
+  <si>
+    <t>PRIVIGEN</t>
+  </si>
+  <si>
+    <t>IMMUNE SERUMS</t>
+  </si>
+  <si>
+    <t>ERLEADA</t>
+  </si>
+  <si>
+    <t>NEXLIZET</t>
+  </si>
+  <si>
+    <t>ACL INHIBITORS &amp; COMBOS</t>
+  </si>
+  <si>
+    <t>RINVOQ</t>
+  </si>
+  <si>
+    <t>DOVATO</t>
+  </si>
+  <si>
+    <t>CREON</t>
+  </si>
+  <si>
+    <t>DIGESTIVE ENZYMES</t>
+  </si>
+  <si>
+    <t>KESIMPTA</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>COSENTYX UNOREADY</t>
+  </si>
+  <si>
+    <t>DESCOVY</t>
+  </si>
+  <si>
+    <t>STIOLTO RESPIMAT</t>
+  </si>
+  <si>
+    <t>IMPAVIDO</t>
+  </si>
+  <si>
+    <t>ANTI-INFECTIVE AGENTS - MISC.</t>
+  </si>
+  <si>
+    <t>COSENTYX SENSOREADY PEN</t>
+  </si>
+  <si>
+    <t>ONETOUCH VERIO TEST STRIPS</t>
+  </si>
+  <si>
     <t>FREESTYLE LIBRE 3 PLUS/SENSOR/GLUCOSE MONITORING SYSTEM</t>
   </si>
   <si>
     <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
   </si>
   <si>
-    <t>Mail</t>
-  </si>
-  <si>
-    <t>SKYRIZI PEN</t>
-  </si>
-  <si>
-    <t>IMMUNOMODULATORS</t>
-  </si>
-  <si>
-    <t>ROZLYTREK</t>
-  </si>
-  <si>
-    <t>ONCOLOGY</t>
-  </si>
-  <si>
-    <t>Non-Specialty</t>
-  </si>
-  <si>
-    <t>SKYRIZI</t>
-  </si>
-  <si>
-    <t>OHTUVAYRE</t>
-  </si>
-  <si>
-    <t>PDE3 &amp; PDE4 INHIBITORS</t>
-  </si>
-  <si>
-    <t>Specialty</t>
-  </si>
-  <si>
-    <t>BREZTRI AEROSPHERE</t>
-  </si>
-  <si>
-    <t>LABA LAMA COMBO</t>
-  </si>
-  <si>
-    <t>NEXLIZET</t>
-  </si>
-  <si>
-    <t>ACL INHIBITORS &amp; COMBOS</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>HUMIRA PEN</t>
-  </si>
-  <si>
-    <t>PRIVIGEN</t>
-  </si>
-  <si>
-    <t>IMMUNE SERUMS</t>
-  </si>
-  <si>
-    <t>TRULICITY</t>
-  </si>
-  <si>
-    <t>KISQALI</t>
-  </si>
-  <si>
-    <t>Generic</t>
-  </si>
-  <si>
-    <t>RINVOQ</t>
-  </si>
-  <si>
-    <t>JUBBONTI</t>
-  </si>
-  <si>
-    <t>OSTEOPOROSIS AGENTS</t>
-  </si>
-  <si>
-    <t>GEMTESA</t>
-  </si>
-  <si>
-    <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+    <t>LYSODREN</t>
+  </si>
+  <si>
+    <t>SPIRIVA RESPIMAT</t>
+  </si>
+  <si>
+    <t>LAMA/ACH</t>
+  </si>
+  <si>
+    <t>NEXLETOL</t>
+  </si>
+  <si>
+    <t>ZENPEP</t>
   </si>
   <si>
     <t>KERENDIA</t>
@@ -203,31 +269,10 @@
     <t>NON-STEROIDAL MINERALOCORTICOID RECEPTOR ANTAGONISTS</t>
   </si>
   <si>
-    <t>ERLEADA</t>
-  </si>
-  <si>
-    <t>LYSODREN</t>
-  </si>
-  <si>
-    <t>CREON</t>
-  </si>
-  <si>
-    <t>DIGESTIVE ENZYMES</t>
-  </si>
-  <si>
-    <t>DESCOVY</t>
-  </si>
-  <si>
-    <t>COSENTYX UNOREADY</t>
-  </si>
-  <si>
-    <t>KESIMPTA</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>COSENTYX SENSOREADY PEN</t>
+    <t>PAXLOVID</t>
+  </si>
+  <si>
+    <t>MISC. ANTIVIRALS</t>
   </si>
   <si>
     <t>WEZLANA</t>
@@ -239,117 +284,75 @@
     <t>MIGRAINE PRODUCTS</t>
   </si>
   <si>
-    <t>IMPAVIDO</t>
-  </si>
-  <si>
-    <t>ANTI-INFECTIVE AGENTS - MISC.</t>
-  </si>
-  <si>
-    <t>ZENPEP</t>
-  </si>
-  <si>
-    <t>BIMZELX</t>
-  </si>
-  <si>
-    <t>OMNIPOD 5 DEXCOM G7G6 PODS (GEN 5)</t>
-  </si>
-  <si>
-    <t>INSULIN ADMINISTRATION SUPPLIES</t>
-  </si>
-  <si>
-    <t>GENVOYA</t>
-  </si>
-  <si>
-    <t>PAXLOVID</t>
-  </si>
-  <si>
-    <t>MISC. ANTIVIRALS</t>
-  </si>
-  <si>
-    <t>ACTEMRA ACTPEN</t>
+    <t>TRIUMEQ</t>
   </si>
   <si>
     <t>PROLIA</t>
   </si>
   <si>
-    <t>TREMFYA</t>
-  </si>
-  <si>
-    <t>LOKELMA</t>
+    <t>TRESIBA FLEXTOUCH</t>
+  </si>
+  <si>
+    <t>BASAL INSULIN</t>
+  </si>
+  <si>
+    <t>Overall - Brand Only</t>
+  </si>
+  <si>
+    <t>Brand Scripts</t>
+  </si>
+  <si>
+    <t>Base Yr</t>
+  </si>
+  <si>
+    <t>Excl - Brand</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>R90</t>
+  </si>
+  <si>
+    <t>OTCs</t>
+  </si>
+  <si>
+    <t>Devices</t>
+  </si>
+  <si>
+    <t>Vaccines</t>
+  </si>
+  <si>
+    <t>Repackaged</t>
+  </si>
+  <si>
+    <t>MSBs</t>
+  </si>
+  <si>
+    <t>Non FDA Approved</t>
+  </si>
+  <si>
+    <t>LDD</t>
+  </si>
+  <si>
+    <t>Institutional NDCs</t>
+  </si>
+  <si>
+    <t>Formulary Exclusions</t>
+  </si>
+  <si>
+    <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
+  </si>
+  <si>
+    <t>Synthroid</t>
+  </si>
+  <si>
+    <t>Misc</t>
   </si>
   <si>
     <t>POTASSIUM REMOVING AGENTS</t>
   </si>
   <si>
-    <t>SYMTUZA</t>
-  </si>
-  <si>
-    <t>AIMOVIG</t>
-  </si>
-  <si>
-    <t>CIMZIA</t>
-  </si>
-  <si>
-    <t>Overall - Brand Only</t>
-  </si>
-  <si>
-    <t>Brand Scripts</t>
-  </si>
-  <si>
-    <t>Base Yr</t>
-  </si>
-  <si>
-    <t>Excl - Brand</t>
-  </si>
-  <si>
-    <t>R30</t>
-  </si>
-  <si>
-    <t>R90</t>
-  </si>
-  <si>
-    <t>OTCs</t>
-  </si>
-  <si>
-    <t>Devices</t>
-  </si>
-  <si>
-    <t>Vaccines</t>
-  </si>
-  <si>
-    <t>Repackaged</t>
-  </si>
-  <si>
-    <t>MSBs</t>
-  </si>
-  <si>
-    <t>Non FDA Approved</t>
-  </si>
-  <si>
-    <t>LDD</t>
-  </si>
-  <si>
-    <t>BASAL INSULIN</t>
-  </si>
-  <si>
-    <t>Institutional NDCs</t>
-  </si>
-  <si>
-    <t>Formulary Exclusions</t>
-  </si>
-  <si>
-    <t>OPHTHALMICS - RHO KINASE INHIBITOR &amp; COMBOS</t>
-  </si>
-  <si>
-    <t>Synthroid</t>
-  </si>
-  <si>
-    <t>Misc</t>
-  </si>
-  <si>
-    <t>LAMA/ACH</t>
-  </si>
-  <si>
     <t>OPIOID AGONISTS &amp; COMBOS</t>
   </si>
   <si>
@@ -359,13 +362,13 @@
     <t>MFP 2026 &amp; 2027</t>
   </si>
   <si>
-    <t>VASOACTIVE SGC STIMULATOR</t>
+    <t>SEDATIVE HYPNOTICS</t>
   </si>
   <si>
     <t>ENTER DESC</t>
   </si>
   <si>
-    <t>BASAL &amp; GLP-1 COMBO</t>
+    <t>OPHTHALMIC PROSTAGLANDINS</t>
   </si>
   <si>
     <t>Non-Rebatable</t>
@@ -374,10 +377,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>RAPID ACTING</t>
-  </si>
-  <si>
-    <t>VAGINAL ESTROGENS</t>
+    <t>ANTIARRHYTHMICS</t>
   </si>
   <si>
     <t>Excl - Generic</t>
@@ -760,7 +760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21F1E43F-0E40-493D-BA95-FF57BCE56F77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BE0E88-5572-4E65-99D8-50C249049E74}">
   <dimension ref="A15:AN129"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -774,7 +774,7 @@
         <v>45658</v>
       </c>
       <c r="AF17">
-        <v>2031</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="18" spans="2:40" x14ac:dyDescent="0.35">
@@ -882,10 +882,10 @@
         <v>19</v>
       </c>
       <c r="AH25">
-        <v>10848588.390509943</v>
+        <v>4485152.5720088715</v>
       </c>
       <c r="AI25">
-        <v>14046.488619590498</v>
+        <v>6502.9916100801247</v>
       </c>
       <c r="AK25">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>21</v>
       </c>
       <c r="AN25">
-        <v>118.8701134849275</v>
+        <v>101.36430581701825</v>
       </c>
     </row>
     <row r="26" spans="2:40" x14ac:dyDescent="0.35">
@@ -929,10 +929,10 @@
         <v>24</v>
       </c>
       <c r="AH26">
-        <v>1749400.9451681029</v>
+        <v>846073.33804573584</v>
       </c>
       <c r="AI26">
-        <v>1243.5793839730713</v>
+        <v>189.4409895539809</v>
       </c>
       <c r="AK26">
         <v>2</v>
@@ -944,7 +944,7 @@
         <v>26</v>
       </c>
       <c r="AN26">
-        <v>1959.5630712041268</v>
+        <v>73.871225708355581</v>
       </c>
     </row>
     <row r="27" spans="2:40" x14ac:dyDescent="0.35">
@@ -976,10 +976,10 @@
         <v>29</v>
       </c>
       <c r="AH27">
-        <v>1278546.0237318398</v>
+        <v>684422.77088101907</v>
       </c>
       <c r="AI27">
-        <v>124.49094484841569</v>
+        <v>1210.9130033444717</v>
       </c>
       <c r="AK27">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>31</v>
       </c>
       <c r="AN27">
-        <v>11.423556462967193</v>
+        <v>9.1806234214884554</v>
       </c>
     </row>
     <row r="28" spans="2:40" x14ac:dyDescent="0.35">
@@ -1020,25 +1020,25 @@
         <v>33</v>
       </c>
       <c r="AG28" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AH28">
-        <v>1063766.4970814695</v>
+        <v>679878.58398656105</v>
       </c>
       <c r="AI28">
-        <v>92.685587658798042</v>
+        <v>580.70099129395476</v>
       </c>
       <c r="AK28">
         <v>4</v>
       </c>
       <c r="AL28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AM28" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AN28">
-        <v>72.16289384454069</v>
+        <v>12.623357204546625</v>
       </c>
     </row>
     <row r="29" spans="2:40" x14ac:dyDescent="0.35">
@@ -1067,30 +1067,30 @@
         <v>37</v>
       </c>
       <c r="AG29" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AH29">
-        <v>969024.95724452497</v>
+        <v>562819.203762886</v>
       </c>
       <c r="AI29">
-        <v>1450.0151454468141</v>
+        <v>67.704953554572768</v>
       </c>
       <c r="AK29">
         <v>5</v>
       </c>
       <c r="AL29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM29" t="s">
         <v>39</v>
       </c>
-      <c r="AM29" t="s">
-        <v>40</v>
-      </c>
       <c r="AN29">
-        <v>260.2205758041319</v>
+        <v>33.444430655818408</v>
       </c>
     </row>
     <row r="30" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D30">
         <v>50455</v>
@@ -1111,28 +1111,28 @@
         <v>6</v>
       </c>
       <c r="AF30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AG30" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AH30">
-        <v>939863.20187687688</v>
+        <v>510027.44919129118</v>
       </c>
       <c r="AI30">
-        <v>207.80235723186348</v>
+        <v>758.17767799447336</v>
       </c>
       <c r="AK30">
         <v>6</v>
       </c>
       <c r="AL30" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM30" t="s">
         <v>43</v>
       </c>
-      <c r="AM30" t="s">
-        <v>44</v>
-      </c>
       <c r="AN30">
-        <v>17.279217660002235</v>
+        <v>630.70316003001471</v>
       </c>
     </row>
     <row r="31" spans="2:40" x14ac:dyDescent="0.35">
@@ -1140,16 +1140,16 @@
         <v>7</v>
       </c>
       <c r="AF31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG31" t="s">
         <v>45</v>
       </c>
-      <c r="AG31" t="s">
-        <v>19</v>
-      </c>
       <c r="AH31">
-        <v>872627.05009166733</v>
+        <v>429443.73220410955</v>
       </c>
       <c r="AI31">
-        <v>1161.3361714452512</v>
+        <v>682.85895050417707</v>
       </c>
       <c r="AK31">
         <v>7</v>
@@ -1158,42 +1158,42 @@
         <v>46</v>
       </c>
       <c r="AM31" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="AN31">
-        <v>8.6666834027757602</v>
+        <v>79.445265332989791</v>
       </c>
     </row>
     <row r="32" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE32">
         <v>8</v>
       </c>
       <c r="AF32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AG32" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AH32">
-        <v>630970.54590877029</v>
+        <v>369203.97937168414</v>
       </c>
       <c r="AI32">
-        <v>160.11949385658573</v>
+        <v>45.781735336479287</v>
       </c>
       <c r="AK32">
         <v>8</v>
       </c>
       <c r="AL32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AM32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AN32">
-        <v>87.427346414385283</v>
+        <v>11.234411025147905</v>
       </c>
     </row>
     <row r="33" spans="2:40" x14ac:dyDescent="0.35">
@@ -1219,16 +1219,16 @@
         <v>9</v>
       </c>
       <c r="AF33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AG33" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="AH33">
-        <v>499027.60181979043</v>
+        <v>313194.45772430557</v>
       </c>
       <c r="AI33">
-        <v>680.89834551876334</v>
+        <v>71.149831516535528</v>
       </c>
       <c r="AK33">
         <v>9</v>
@@ -1240,7 +1240,7 @@
         <v>54</v>
       </c>
       <c r="AN33">
-        <v>120.88987379876993</v>
+        <v>162.92897553435017</v>
       </c>
     </row>
     <row r="34" spans="2:40" x14ac:dyDescent="0.35">
@@ -1269,13 +1269,13 @@
         <v>55</v>
       </c>
       <c r="AG34" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="AH34">
-        <v>486031.03453443677</v>
+        <v>242906.60097460437</v>
       </c>
       <c r="AI34">
-        <v>88.532562587995756</v>
+        <v>80.220098415227724</v>
       </c>
       <c r="AK34">
         <v>10</v>
@@ -1284,10 +1284,10 @@
         <v>56</v>
       </c>
       <c r="AM34" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="AN34">
-        <v>11.381422665321466</v>
+        <v>35.967979483458087</v>
       </c>
     </row>
     <row r="35" spans="2:40" x14ac:dyDescent="0.35">
@@ -1319,10 +1319,10 @@
         <v>58</v>
       </c>
       <c r="AH35">
-        <v>287790.8057999548</v>
+        <v>210371.49378127669</v>
       </c>
       <c r="AI35">
-        <v>205.70791132533245</v>
+        <v>183.27796333713027</v>
       </c>
       <c r="AK35">
         <v>11</v>
@@ -1331,10 +1331,10 @@
         <v>59</v>
       </c>
       <c r="AM35" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AN35">
-        <v>37.474218682433957</v>
+        <v>8.8389913539470193</v>
       </c>
     </row>
     <row r="36" spans="2:40" x14ac:dyDescent="0.35">
@@ -1360,28 +1360,28 @@
         <v>12</v>
       </c>
       <c r="AF36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AG36" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AH36">
-        <v>249571.00330962657</v>
+        <v>196882.51426775099</v>
       </c>
       <c r="AI36">
-        <v>46.276637637323475</v>
+        <v>42.539720343718628</v>
       </c>
       <c r="AK36">
         <v>12</v>
       </c>
       <c r="AL36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AM36" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="AN36">
-        <v>6.9794265239172892</v>
+        <v>35.967979483458087</v>
       </c>
     </row>
     <row r="37" spans="2:40" x14ac:dyDescent="0.35">
@@ -1413,10 +1413,10 @@
         <v>29</v>
       </c>
       <c r="AH37">
-        <v>192842.19107443519</v>
+        <v>172281.35200929941</v>
       </c>
       <c r="AI37">
-        <v>39.706923453259122</v>
+        <v>389.26153166872513</v>
       </c>
       <c r="AK37">
         <v>13</v>
@@ -1425,15 +1425,15 @@
         <v>64</v>
       </c>
       <c r="AM37" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AN37">
-        <v>2.2728427289926008</v>
+        <v>1.8442945375034703</v>
       </c>
     </row>
     <row r="38" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D38">
         <v>437939</v>
@@ -1454,16 +1454,16 @@
         <v>14</v>
       </c>
       <c r="AF38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG38" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="AH38">
-        <v>167270.19921367153</v>
+        <v>145976.16203905191</v>
       </c>
       <c r="AI38">
-        <v>274.17645257954888</v>
+        <v>36.416828676815115</v>
       </c>
       <c r="AK38">
         <v>14</v>
@@ -1472,10 +1472,10 @@
         <v>67</v>
       </c>
       <c r="AM38" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="AN38">
-        <v>1.4829118397744609</v>
+        <v>649.12112980297104</v>
       </c>
     </row>
     <row r="39" spans="2:40" x14ac:dyDescent="0.35">
@@ -1483,16 +1483,16 @@
         <v>15</v>
       </c>
       <c r="AF39" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG39" t="s">
         <v>69</v>
       </c>
-      <c r="AG39" t="s">
-        <v>58</v>
-      </c>
       <c r="AH39">
-        <v>166414.7962048185</v>
+        <v>129444.43439370711</v>
       </c>
       <c r="AI39">
-        <v>46.643072916790494</v>
+        <v>1776.7923780969579</v>
       </c>
       <c r="AK39">
         <v>15</v>
@@ -1501,15 +1501,15 @@
         <v>70</v>
       </c>
       <c r="AM39" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AN39">
-        <v>3.4092640934889014</v>
+        <v>11.879830145059112</v>
       </c>
     </row>
     <row r="40" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AE40">
         <v>16</v>
@@ -1521,10 +1521,10 @@
         <v>72</v>
       </c>
       <c r="AH40">
-        <v>162953.20687073565</v>
+        <v>127944.83410841081</v>
       </c>
       <c r="AI40">
-        <v>389.34942847232037</v>
+        <v>326.64242576035286</v>
       </c>
       <c r="AK40">
         <v>16</v>
@@ -1533,10 +1533,10 @@
         <v>73</v>
       </c>
       <c r="AM40" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="AN40">
-        <v>3.8345197898363708</v>
+        <v>84.671751065095364</v>
       </c>
     </row>
     <row r="41" spans="2:40" x14ac:dyDescent="0.35">
@@ -1565,25 +1565,25 @@
         <v>74</v>
       </c>
       <c r="AG41" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="AH41">
-        <v>140413.12798845579</v>
+        <v>125277.02134152722</v>
       </c>
       <c r="AI41">
-        <v>388.11934797469178</v>
+        <v>41.557212617140003</v>
       </c>
       <c r="AK41">
         <v>17</v>
       </c>
       <c r="AL41" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM41" t="s">
         <v>76</v>
       </c>
-      <c r="AM41" t="s">
-        <v>29</v>
-      </c>
       <c r="AN41">
-        <v>12.27335073656004</v>
+        <v>75.691413830918577</v>
       </c>
     </row>
     <row r="42" spans="2:40" x14ac:dyDescent="0.35">
@@ -1612,25 +1612,25 @@
         <v>77</v>
       </c>
       <c r="AG42" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="AH42">
-        <v>128359.46543945617</v>
+        <v>123126.77103968868</v>
       </c>
       <c r="AI42">
-        <v>262.28203924315585</v>
+        <v>397.30740313412866</v>
       </c>
       <c r="AK42">
         <v>18</v>
       </c>
       <c r="AL42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM42" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AN42">
-        <v>3.4092640934889005</v>
+        <v>2.0893068082072435</v>
       </c>
     </row>
     <row r="43" spans="2:40" x14ac:dyDescent="0.35">
@@ -1656,28 +1656,28 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG43" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH43">
-        <v>121172.71055050124</v>
+        <v>96889.64743070594</v>
       </c>
       <c r="AI43">
-        <v>151.6245874764233</v>
+        <v>204.01271371025948</v>
       </c>
       <c r="AK43">
         <v>19</v>
       </c>
       <c r="AL43" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s">
         <v>21</v>
       </c>
       <c r="AN43">
-        <v>8.947212842951533</v>
+        <v>13.079265266712031</v>
       </c>
     </row>
     <row r="44" spans="2:40" x14ac:dyDescent="0.35">
@@ -1703,28 +1703,28 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG44" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="AH44">
-        <v>104347.41443705001</v>
+        <v>89156.439539307932</v>
       </c>
       <c r="AI44">
-        <v>209.19821815318181</v>
+        <v>238.33579599896936</v>
       </c>
       <c r="AK44">
         <v>20</v>
       </c>
       <c r="AL44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM44" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="AN44">
-        <v>5.4548225495822447</v>
+        <v>473.63438297690965</v>
       </c>
     </row>
     <row r="45" spans="2:40" x14ac:dyDescent="0.35">
@@ -1749,7 +1749,7 @@
     </row>
     <row r="46" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D46">
         <v>488394</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="47" spans="2:40" x14ac:dyDescent="0.35">
       <c r="AE47" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="2:40" x14ac:dyDescent="0.35">
@@ -1783,7 +1783,7 @@
         <v>15</v>
       </c>
       <c r="AH48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="2:34" x14ac:dyDescent="0.35">
@@ -1794,10 +1794,10 @@
         <v>19</v>
       </c>
       <c r="AG49">
-        <v>11721215.440601612</v>
+        <v>4995180.0212001624</v>
       </c>
       <c r="AH49">
-        <v>15207.824791035748</v>
+        <v>7261.1692880745968</v>
       </c>
     </row>
     <row r="50" spans="2:34" x14ac:dyDescent="0.35">
@@ -1805,18 +1805,18 @@
         <v>2</v>
       </c>
       <c r="AF50" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AG50">
-        <v>4640550.2464817502</v>
+        <v>2605823.1494742087</v>
       </c>
       <c r="AH50">
-        <v>828.41945221214235</v>
+        <v>612.62591821724834</v>
       </c>
     </row>
     <row r="51" spans="2:34" x14ac:dyDescent="0.35">
       <c r="D51" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J51">
         <v>2027</v>
@@ -1831,24 +1831,24 @@
         <v>3</v>
       </c>
       <c r="AF51" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AG51">
-        <v>1749400.9451681029</v>
+        <v>874429.25547745102</v>
       </c>
       <c r="AH51">
-        <v>1249.8898753325686</v>
+        <v>1746.4240735449837</v>
       </c>
     </row>
     <row r="52" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D52" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E52" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F52" t="s">
         <v>27</v>
@@ -1857,13 +1857,13 @@
         <v>36</v>
       </c>
       <c r="H52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J52" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L52" t="s">
         <v>27</v>
@@ -1872,13 +1872,13 @@
         <v>36</v>
       </c>
       <c r="N52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P52" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q52" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="R52" t="s">
         <v>27</v>
@@ -1887,13 +1887,13 @@
         <v>36</v>
       </c>
       <c r="T52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V52" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="W52" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="X52" t="s">
         <v>27</v>
@@ -1902,24 +1902,24 @@
         <v>36</v>
       </c>
       <c r="Z52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AE52">
         <v>4</v>
       </c>
       <c r="AF52" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG52">
-        <v>977368.58087656915</v>
+        <v>679878.58398656105</v>
       </c>
       <c r="AH52">
-        <v>1591.449898611768</v>
+        <v>586.01253147588625</v>
       </c>
     </row>
     <row r="53" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D53">
         <v>1347</v>
@@ -1985,18 +1985,18 @@
         <v>5</v>
       </c>
       <c r="AF53" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AG53">
-        <v>499027.60181979043</v>
+        <v>429443.73220410955</v>
       </c>
       <c r="AH53">
-        <v>680.92865256678351</v>
+        <v>683.22351343052196</v>
       </c>
     </row>
     <row r="54" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2062,18 +2062,18 @@
         <v>6</v>
       </c>
       <c r="AF54" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="AG54">
-        <v>486031.03453443677</v>
+        <v>335648.51512280386</v>
       </c>
       <c r="AH54">
-        <v>124.20250111458043</v>
+        <v>224.83517595427031</v>
       </c>
     </row>
     <row r="55" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D55">
         <v>9389</v>
@@ -2139,18 +2139,18 @@
         <v>7</v>
       </c>
       <c r="AF55" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="AG55">
-        <v>454205.60200477333</v>
+        <v>313194.45772430557</v>
       </c>
       <c r="AH55">
-        <v>252.35098424212296</v>
+        <v>112.86668778143213</v>
       </c>
     </row>
     <row r="56" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2216,18 +2216,18 @@
         <v>8</v>
       </c>
       <c r="AF56" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="AG56">
-        <v>417295.3443087897</v>
+        <v>246812.7075960777</v>
       </c>
       <c r="AH56">
-        <v>614.91597457147384</v>
+        <v>457.55452554670916</v>
       </c>
     </row>
     <row r="57" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D57">
         <v>2931</v>
@@ -2296,15 +2296,15 @@
         <v>72</v>
       </c>
       <c r="AG57">
-        <v>249760.06234919047</v>
+        <v>179197.82347819317</v>
       </c>
       <c r="AH57">
-        <v>534.40117633455736</v>
+        <v>462.50869117195208</v>
       </c>
     </row>
     <row r="58" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2370,18 +2370,18 @@
         <v>10</v>
       </c>
       <c r="AF58" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG58">
-        <v>167560.8225097525</v>
+        <v>164356.46290339506</v>
       </c>
       <c r="AH58">
-        <v>462.23259030151735</v>
+        <v>1638.1229069219519</v>
       </c>
     </row>
     <row r="59" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2447,18 +2447,18 @@
         <v>11</v>
       </c>
       <c r="AF59" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AG59">
-        <v>161828.24282291581</v>
+        <v>146932.2941803307</v>
       </c>
       <c r="AH59">
-        <v>1358.1759373457792</v>
+        <v>473.17514845622355</v>
       </c>
     </row>
     <row r="60" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2524,18 +2524,18 @@
         <v>12</v>
       </c>
       <c r="AF60" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="AG60">
-        <v>128359.46543945617</v>
+        <v>138404.1071528391</v>
       </c>
       <c r="AH60">
-        <v>361.81659976398367</v>
+        <v>1894.1177522604098</v>
       </c>
     </row>
     <row r="61" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D61">
         <v>2579</v>
@@ -2601,18 +2601,18 @@
         <v>13</v>
       </c>
       <c r="AF61" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG61">
-        <v>128030.64384726433</v>
+        <v>104126.40020492363</v>
       </c>
       <c r="AH61">
-        <v>261.54191399465503</v>
+        <v>272.13848640839586</v>
       </c>
     </row>
     <row r="62" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2678,18 +2678,18 @@
         <v>14</v>
       </c>
       <c r="AF62" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="AG62">
-        <v>121172.71055050124</v>
+        <v>89156.439539307932</v>
       </c>
       <c r="AH62">
-        <v>163.62700541277491</v>
+        <v>330.50853220764293</v>
       </c>
     </row>
     <row r="63" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D63">
         <v>1695</v>
@@ -2755,13 +2755,13 @@
         <v>15</v>
       </c>
       <c r="AF63" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG63">
-        <v>81831.517903844724</v>
+        <v>81733.859441732639</v>
       </c>
       <c r="AH63">
-        <v>178.33393801672457</v>
+        <v>130.85634255514734</v>
       </c>
     </row>
     <row r="64" spans="2:34" x14ac:dyDescent="0.35">
@@ -2832,21 +2832,21 @@
         <v>16</v>
       </c>
       <c r="AF64" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG64">
-        <v>61024.565837317859</v>
+        <v>74140.7628796348</v>
       </c>
       <c r="AH64">
-        <v>113.69076064051974</v>
+        <v>182.48153556202558</v>
       </c>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2912,18 +2912,18 @@
         <v>17</v>
       </c>
       <c r="AF65" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG65">
-        <v>45072.304062149582</v>
+        <v>73409.458195921135</v>
       </c>
       <c r="AH65">
-        <v>53.273503707932505</v>
+        <v>178.16096038339265</v>
       </c>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2989,33 +2989,33 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG66">
-        <v>41613.597077005179</v>
+        <v>73146.309046075505</v>
       </c>
       <c r="AH66">
-        <v>41.276696829923722</v>
+        <v>229.43412048369808</v>
       </c>
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J67">
         <v>1900.2780590668344</v>
@@ -3066,18 +3066,18 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG67">
-        <v>35406.02786434695</v>
+        <v>72979.478651104262</v>
       </c>
       <c r="AH67">
-        <v>247.39758596977751</v>
+        <v>108.14135476051091</v>
       </c>
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D68">
         <v>17941</v>
@@ -3143,13 +3143,13 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="AG68">
-        <v>33594.024089228646</v>
+        <v>67946.467271327012</v>
       </c>
       <c r="AH68">
-        <v>159.50857713442161</v>
+        <v>188.81633688221089</v>
       </c>
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.35">
@@ -3157,10 +3157,10 @@
         <v>114</v>
       </c>
       <c r="D70" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E70" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F70" t="s">
         <v>27</v>
@@ -3169,13 +3169,13 @@
         <v>36</v>
       </c>
       <c r="H70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J70" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L70" t="s">
         <v>27</v>
@@ -3184,13 +3184,13 @@
         <v>36</v>
       </c>
       <c r="N70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P70" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q70" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="R70" t="s">
         <v>27</v>
@@ -3199,13 +3199,13 @@
         <v>36</v>
       </c>
       <c r="T70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V70" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="W70" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="X70" t="s">
         <v>27</v>
@@ -3214,12 +3214,12 @@
         <v>36</v>
       </c>
       <c r="Z70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D71">
         <v>7</v>
@@ -3284,7 +3284,7 @@
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3349,7 +3349,7 @@
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3479,7 +3479,7 @@
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D75">
         <v>2421</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="78" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3739,7 +3739,7 @@
     </row>
     <row r="79" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D79">
         <v>2006</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="80" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="81" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -4002,7 +4002,7 @@
         <v>115</v>
       </c>
       <c r="B83" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -4067,7 +4067,7 @@
     </row>
     <row r="84" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -4132,22 +4132,22 @@
     </row>
     <row r="85" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D85" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E85" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F85" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G85" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H85" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J85">
         <v>212099.45937868423</v>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="86" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D86">
         <v>4434</v>
@@ -4265,10 +4265,10 @@
         <v>116</v>
       </c>
       <c r="D88" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E88" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F88" t="s">
         <v>27</v>
@@ -4277,13 +4277,13 @@
         <v>36</v>
       </c>
       <c r="H88" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J88" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K88" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L88" t="s">
         <v>27</v>
@@ -4292,13 +4292,13 @@
         <v>36</v>
       </c>
       <c r="N88" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P88" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q88" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="R88" t="s">
         <v>27</v>
@@ -4307,13 +4307,13 @@
         <v>36</v>
       </c>
       <c r="T88" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V88" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="W88" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="X88" t="s">
         <v>27</v>
@@ -4322,12 +4322,12 @@
         <v>36</v>
       </c>
       <c r="Z88" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D89">
         <v>1354</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="90" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -4457,7 +4457,7 @@
     </row>
     <row r="91" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D91">
         <v>9389</v>
@@ -4522,7 +4522,7 @@
     </row>
     <row r="92" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -4587,7 +4587,7 @@
     </row>
     <row r="93" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D93">
         <v>5352</v>
@@ -4652,7 +4652,7 @@
     </row>
     <row r="94" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -4717,7 +4717,7 @@
     </row>
     <row r="95" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -4782,7 +4782,7 @@
     </row>
     <row r="96" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="97" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D97">
         <v>4585</v>
@@ -4912,7 +4912,7 @@
     </row>
     <row r="98" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="99" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D99">
         <v>1695</v>
@@ -5110,7 +5110,7 @@
         <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -5175,7 +5175,7 @@
     </row>
     <row r="102" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -5240,22 +5240,22 @@
     </row>
     <row r="103" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D103" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E103" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F103" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G103" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H103" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J103">
         <v>213999.73743775106</v>
@@ -5305,7 +5305,7 @@
     </row>
     <row r="104" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D104">
         <v>22375</v>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="108" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H108">
         <v>523801</v>
